--- a/excel-files/LAS PINAS/GOLDEN ACRES NATIONAL HIGH SCHOOL.xlsx
+++ b/excel-files/LAS PINAS/GOLDEN ACRES NATIONAL HIGH SCHOOL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="113" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D52B528D-21BE-4D0E-AB88-283BC0E0EB32}"/>
+  <xr:revisionPtr revIDLastSave="268" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9ACE9569-4DD4-4C6C-BEE8-DB6FB29CDD65}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TextBooks" sheetId="1" r:id="rId1"/>
@@ -5340,15 +5340,12 @@
     <protectedRange sqref="F1:F98" name="SOURCE"/>
   </protectedRanges>
   <phoneticPr fontId="8" type="noConversion"/>
-  <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E91:E98" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E91:E98 E2:E6 E8:E12 E14:E19 E21:E29 E31:E39 E41:E49 E51:E59 E61:E69 E71:E79 E81:E89" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
       <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F21:F29 F31:F39 F41:F49 F51:F59 F61:F69 F71:F79 F81:F89 F2:F6 F8:F12 F91:F98" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
       <formula1>"CO,RO,SDO"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E6 E8:E12 E14:E19 E21:E29 E31:E39 E41:E49 E51:E59 E61:E69 E71:E79 E81:E89" xr:uid="{5B344349-8837-4EE9-B5EC-A95CABA2D26B}">
-      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5360,7 +5357,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0858F8C8-8AF8-4852-B88C-61047AF726C8}">
-  <dimension ref="A1:AA157"/>
+  <dimension ref="A1:AA127"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -5654,7 +5651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="19.149999999999999">
+    <row r="6" spans="1:27" ht="19.5">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -5723,7 +5720,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="19.149999999999999">
+    <row r="7" spans="1:27" ht="19.5">
       <c r="A7" s="1">
         <v>1</v>
       </c>
@@ -5792,7 +5789,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="19.149999999999999">
+    <row r="8" spans="1:27" ht="19.5">
       <c r="A8" s="1">
         <v>1</v>
       </c>
@@ -5861,7 +5858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="19.149999999999999">
+    <row r="9" spans="1:27" ht="19.5">
       <c r="A9" s="1">
         <v>1</v>
       </c>
@@ -5930,7 +5927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="19.149999999999999">
+    <row r="10" spans="1:27" ht="19.5">
       <c r="A10" s="1">
         <v>1</v>
       </c>
@@ -5999,7 +5996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="19.149999999999999">
+    <row r="11" spans="1:27" ht="19.5">
       <c r="A11" s="1">
         <v>1</v>
       </c>
@@ -6068,7 +6065,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="19.149999999999999">
+    <row r="12" spans="1:27" ht="19.5">
       <c r="A12" s="1">
         <v>1</v>
       </c>
@@ -6219,7 +6216,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="19.149999999999999">
+    <row r="15" spans="1:27" ht="19.5">
       <c r="A15" s="1">
         <v>2</v>
       </c>
@@ -6288,7 +6285,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="19.149999999999999">
+    <row r="16" spans="1:27" ht="19.5">
       <c r="A16" s="1">
         <v>2</v>
       </c>
@@ -6357,7 +6354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="19.149999999999999">
+    <row r="17" spans="1:27" ht="19.5">
       <c r="A17" s="1">
         <v>2</v>
       </c>
@@ -6426,7 +6423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="19.149999999999999">
+    <row r="18" spans="1:27" ht="19.5">
       <c r="A18" s="1">
         <v>2</v>
       </c>
@@ -6495,7 +6492,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="19.149999999999999">
+    <row r="19" spans="1:27" ht="19.5">
       <c r="A19" s="1">
         <v>2</v>
       </c>
@@ -6564,7 +6561,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="19.149999999999999">
+    <row r="20" spans="1:27" ht="19.5">
       <c r="A20" s="1">
         <v>2</v>
       </c>
@@ -6633,7 +6630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="19.149999999999999">
+    <row r="21" spans="1:27" ht="19.5">
       <c r="A21" s="1">
         <v>2</v>
       </c>
@@ -6785,7 +6782,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="19.149999999999999">
+    <row r="24" spans="1:27" ht="19.5">
       <c r="A24" s="1">
         <v>3</v>
       </c>
@@ -6854,7 +6851,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="19.149999999999999">
+    <row r="25" spans="1:27" ht="19.5">
       <c r="A25" s="1">
         <v>3</v>
       </c>
@@ -6923,7 +6920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="19.149999999999999">
+    <row r="26" spans="1:27" ht="19.5">
       <c r="A26" s="1">
         <v>3</v>
       </c>
@@ -6992,7 +6989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="19.149999999999999">
+    <row r="27" spans="1:27" ht="19.5">
       <c r="A27" s="1">
         <v>3</v>
       </c>
@@ -7061,7 +7058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="19.149999999999999">
+    <row r="28" spans="1:27" ht="19.5">
       <c r="A28" s="1">
         <v>3</v>
       </c>
@@ -7130,7 +7127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="19.149999999999999">
+    <row r="29" spans="1:27" ht="19.5">
       <c r="A29" s="1">
         <v>3</v>
       </c>
@@ -7199,7 +7196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:27" ht="19.149999999999999">
+    <row r="30" spans="1:27" ht="19.5">
       <c r="A30" s="1">
         <v>3</v>
       </c>
@@ -7268,7 +7265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:27" ht="19.149999999999999">
+    <row r="31" spans="1:27" ht="19.5">
       <c r="A31" s="1">
         <v>3</v>
       </c>
@@ -7420,7 +7417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="19.149999999999999">
+    <row r="34" spans="1:27" ht="19.5">
       <c r="A34" s="1">
         <v>4</v>
       </c>
@@ -7489,7 +7486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="19.149999999999999">
+    <row r="35" spans="1:27" ht="19.5">
       <c r="A35" s="1">
         <v>4</v>
       </c>
@@ -7558,7 +7555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="19.149999999999999">
+    <row r="36" spans="1:27" ht="19.5">
       <c r="A36" s="1">
         <v>4</v>
       </c>
@@ -7627,7 +7624,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="19.149999999999999">
+    <row r="37" spans="1:27" ht="38.25">
       <c r="A37" s="1">
         <v>4</v>
       </c>
@@ -7696,7 +7693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="19.149999999999999">
+    <row r="38" spans="1:27" ht="19.5">
       <c r="A38" s="1">
         <v>4</v>
       </c>
@@ -7765,7 +7762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="19.149999999999999">
+    <row r="39" spans="1:27" ht="19.5">
       <c r="A39" s="1">
         <v>4</v>
       </c>
@@ -7834,7 +7831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="19.149999999999999">
+    <row r="40" spans="1:27" ht="19.5">
       <c r="A40" s="1">
         <v>4</v>
       </c>
@@ -7903,7 +7900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="19.149999999999999">
+    <row r="41" spans="1:27" ht="19.5">
       <c r="A41" s="1">
         <v>4</v>
       </c>
@@ -8055,7 +8052,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="19.149999999999999">
+    <row r="44" spans="1:27" ht="19.5">
       <c r="A44" s="1">
         <v>5</v>
       </c>
@@ -8124,7 +8121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="19.149999999999999">
+    <row r="45" spans="1:27" ht="19.5">
       <c r="A45" s="1">
         <v>5</v>
       </c>
@@ -8193,7 +8190,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="19.149999999999999">
+    <row r="46" spans="1:27" ht="19.5">
       <c r="A46" s="1">
         <v>5</v>
       </c>
@@ -8262,7 +8259,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="19.149999999999999">
+    <row r="47" spans="1:27" ht="38.25">
       <c r="A47" s="1">
         <v>5</v>
       </c>
@@ -8331,7 +8328,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="19.149999999999999">
+    <row r="48" spans="1:27" ht="19.5">
       <c r="A48" s="1">
         <v>5</v>
       </c>
@@ -8400,7 +8397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:27" ht="19.149999999999999">
+    <row r="49" spans="1:27" ht="19.5">
       <c r="A49" s="1">
         <v>5</v>
       </c>
@@ -8469,7 +8466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="19.149999999999999">
+    <row r="50" spans="1:27" ht="19.5">
       <c r="A50" s="1">
         <v>5</v>
       </c>
@@ -8538,7 +8535,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="19.149999999999999">
+    <row r="51" spans="1:27" ht="19.5">
       <c r="A51" s="1">
         <v>5</v>
       </c>
@@ -8690,7 +8687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:27" ht="19.149999999999999">
+    <row r="54" spans="1:27" ht="19.5">
       <c r="A54" s="1">
         <v>6</v>
       </c>
@@ -8759,7 +8756,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:27" ht="19.149999999999999">
+    <row r="55" spans="1:27" ht="19.5">
       <c r="A55" s="1">
         <v>6</v>
       </c>
@@ -8828,7 +8825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:27" ht="19.149999999999999">
+    <row r="56" spans="1:27" ht="19.5">
       <c r="A56" s="1">
         <v>6</v>
       </c>
@@ -8897,7 +8894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:27" ht="19.149999999999999">
+    <row r="57" spans="1:27" ht="38.25">
       <c r="A57" s="1">
         <v>6</v>
       </c>
@@ -8966,7 +8963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:27" ht="19.149999999999999">
+    <row r="58" spans="1:27" ht="19.5">
       <c r="A58" s="1">
         <v>6</v>
       </c>
@@ -9035,7 +9032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:27" ht="19.149999999999999">
+    <row r="59" spans="1:27" ht="19.5">
       <c r="A59" s="1">
         <v>6</v>
       </c>
@@ -9104,7 +9101,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:27" ht="19.149999999999999">
+    <row r="60" spans="1:27" ht="19.5">
       <c r="A60" s="1">
         <v>6</v>
       </c>
@@ -9173,7 +9170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:27" ht="19.149999999999999">
+    <row r="61" spans="1:27" ht="19.5">
       <c r="A61" s="1">
         <v>6</v>
       </c>
@@ -11905,7 +11902,7 @@
       <c r="Z102" s="13"/>
       <c r="AA102" s="13"/>
     </row>
-    <row r="103" spans="1:27" ht="38.450000000000003">
+    <row r="103" spans="1:27" ht="38.25">
       <c r="A103" s="1" t="s">
         <v>23</v>
       </c>
@@ -11974,7 +11971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:27" ht="19.149999999999999">
+    <row r="104" spans="1:27" ht="19.5">
       <c r="A104" s="1" t="s">
         <v>23</v>
       </c>
@@ -12043,7 +12040,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:27" ht="19.149999999999999">
+    <row r="105" spans="1:27" ht="19.5">
       <c r="A105" s="1" t="s">
         <v>23</v>
       </c>
@@ -12112,7 +12109,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:27" ht="19.149999999999999">
+    <row r="106" spans="1:27" ht="19.5">
       <c r="A106" s="1" t="s">
         <v>23</v>
       </c>
@@ -12181,7 +12178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:27" ht="38.450000000000003">
+    <row r="107" spans="1:27" ht="38.25">
       <c r="A107" s="1" t="s">
         <v>23</v>
       </c>
@@ -12250,7 +12247,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:27" ht="19.149999999999999">
+    <row r="108" spans="1:27" ht="38.25">
       <c r="A108" s="1" t="s">
         <v>23</v>
       </c>
@@ -12319,7 +12316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:27" ht="38.450000000000003">
+    <row r="109" spans="1:27" ht="57.75">
       <c r="A109" s="1" t="s">
         <v>23</v>
       </c>
@@ -12388,7 +12385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:27" ht="38.450000000000003">
+    <row r="110" spans="1:27" ht="38.25">
       <c r="A110" s="1" t="s">
         <v>23</v>
       </c>
@@ -12457,7 +12454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="111" spans="1:27" s="7" customFormat="1" ht="19.5">
       <c r="J111" s="13"/>
       <c r="N111" s="13"/>
       <c r="O111" s="13"/>
@@ -12468,7 +12465,7 @@
       <c r="Z111" s="13"/>
       <c r="AA111" s="13"/>
     </row>
-    <row r="112" spans="1:27" ht="19.149999999999999">
+    <row r="112" spans="1:27" ht="19.5">
       <c r="A112" s="1"/>
       <c r="B112" s="9"/>
       <c r="C112" s="1"/>
@@ -12530,7 +12527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:27" ht="19.149999999999999">
+    <row r="113" spans="1:27" ht="19.5">
       <c r="A113" s="1"/>
       <c r="B113" s="9"/>
       <c r="C113" s="1"/>
@@ -12592,7 +12589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:27" ht="19.149999999999999">
+    <row r="114" spans="1:27" ht="19.5">
       <c r="A114" s="1"/>
       <c r="B114" s="9"/>
       <c r="C114" s="1"/>
@@ -12654,7 +12651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:27" ht="19.149999999999999">
+    <row r="115" spans="1:27" ht="19.5">
       <c r="A115" s="1"/>
       <c r="B115" s="9"/>
       <c r="C115" s="1"/>
@@ -12716,7 +12713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:27" ht="19.149999999999999">
+    <row r="116" spans="1:27" ht="19.5">
       <c r="A116" s="1"/>
       <c r="B116" s="9"/>
       <c r="C116" s="1"/>
@@ -12778,7 +12775,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:27" ht="19.149999999999999">
+    <row r="117" spans="1:27" ht="19.5">
       <c r="A117" s="1"/>
       <c r="B117" s="9"/>
       <c r="C117" s="1"/>
@@ -12840,7 +12837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:27" ht="19.149999999999999">
+    <row r="118" spans="1:27" ht="19.5">
       <c r="A118" s="1"/>
       <c r="B118" s="9"/>
       <c r="C118" s="1"/>
@@ -12902,7 +12899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:27" ht="19.149999999999999">
+    <row r="119" spans="1:27" ht="19.5">
       <c r="A119" s="1"/>
       <c r="B119" s="9"/>
       <c r="C119" s="1"/>
@@ -12964,7 +12961,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:27" ht="19.149999999999999">
+    <row r="120" spans="1:27" ht="19.5">
       <c r="A120" s="1"/>
       <c r="B120" s="9"/>
       <c r="C120" s="1"/>
@@ -13026,7 +13023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:27" ht="19.149999999999999">
+    <row r="121" spans="1:27" ht="19.5">
       <c r="A121" s="1"/>
       <c r="B121" s="9"/>
       <c r="C121" s="1"/>
@@ -13088,7 +13085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:27" ht="19.149999999999999">
+    <row r="122" spans="1:27" ht="19.5">
       <c r="A122" s="1"/>
       <c r="B122" s="9"/>
       <c r="C122" s="1"/>
@@ -13150,7 +13147,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:27" ht="19.149999999999999">
+    <row r="123" spans="1:27" ht="19.5">
       <c r="A123" s="1"/>
       <c r="B123" s="9"/>
       <c r="C123" s="1"/>
@@ -13212,7 +13209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:27" ht="19.149999999999999">
+    <row r="124" spans="1:27" ht="19.5">
       <c r="A124" s="1"/>
       <c r="B124" s="9"/>
       <c r="C124" s="1"/>
@@ -13274,7 +13271,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:27" ht="19.149999999999999">
+    <row r="125" spans="1:27" ht="19.5">
       <c r="A125" s="1"/>
       <c r="B125" s="9"/>
       <c r="C125" s="1"/>
@@ -13336,7 +13333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:27" ht="19.149999999999999">
+    <row r="126" spans="1:27" ht="19.5">
       <c r="A126" s="1"/>
       <c r="B126" s="9"/>
       <c r="C126" s="1"/>
@@ -13398,7 +13395,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:27" ht="19.149999999999999">
+    <row r="127" spans="1:27" ht="19.5">
       <c r="A127" s="29"/>
       <c r="B127" s="30"/>
       <c r="C127" s="29"/>
@@ -13419,7 +13416,7 @@
         <v>0</v>
       </c>
       <c r="K127" s="31"/>
-      <c r="L127" s="29"/>
+      <c r="L127" s="1"/>
       <c r="M127" s="31"/>
       <c r="N127" s="5">
         <f t="shared" ref="N127" si="24">IF((J127-K127)&lt;0,0,(J127-K127))</f>
@@ -13431,7 +13428,7 @@
       </c>
       <c r="P127" s="5"/>
       <c r="Q127" s="31"/>
-      <c r="R127" s="29"/>
+      <c r="R127" s="1"/>
       <c r="S127" s="31"/>
       <c r="T127" s="5">
         <f t="shared" si="18"/>
@@ -13446,7 +13443,7 @@
         <v>0</v>
       </c>
       <c r="W127" s="31"/>
-      <c r="X127" s="29"/>
+      <c r="X127" s="1"/>
       <c r="Y127" s="31"/>
       <c r="Z127" s="5">
         <f t="shared" si="20"/>
@@ -13457,190 +13454,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:27">
-      <c r="J128" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="129" spans="10:10">
-      <c r="J129" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="130" spans="10:10">
-      <c r="J130" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="131" spans="10:10">
-      <c r="J131" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="132" spans="10:10">
-      <c r="J132" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="133" spans="10:10">
-      <c r="J133" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="134" spans="10:10">
-      <c r="J134" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="135" spans="10:10">
-      <c r="J135" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="136" spans="10:10">
-      <c r="J136" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="137" spans="10:10">
-      <c r="J137" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="138" spans="10:10">
-      <c r="J138" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="139" spans="10:10">
-      <c r="J139" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="140" spans="10:10">
-      <c r="J140" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="141" spans="10:10">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="10:10">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="10:10">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="10:10">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C2:C3 C14:C21 C23:C31 C33:C41 C43:C51 C53:C61 C63:C71 C73:C81 C83:C91 C93:C101 C103:C110 C112:C127 C5:C12" name="Textbooks"/>
-    <protectedRange sqref="J2:L3 D2:F3 H5:L5 D14:F21 Q14:R21 W14:X21 D23:F31 Q23:R31 W23:X31 D33:F41 H33:I41 Q33:R41 W33:X41 D43:F51 H43:I51 Q43:R51 W43:X51 D53:F61 H53:I61 Q53:R61 W53:X61 H63:I71 Q63:R71 W63:X71 H73:I81 Q73:R81 W73:X81 H83:I91 Q83:R91 W83:X91 H93:I101 Q93:R101 W93:X101 D103:F110 H103:I110 Q103:R110 W103:X110 D112:F127 H112:I127 N127:R127 W112:X127 H14:I21 H23:I31 H6:I12 K6:L12 K33:L41 K43:L51 K53:L61 K63:L71 K73:L81 K83:L91 K93:L101 K103:L110 K112:L127 K14:L21 K23:L31 Q112:R126 P2:R2 V2:X3 N13:P126 T13:V127 J6:J127 D5:F12 N5:R12 T5:X12 N4:P4 T4:V4 J4 Z4:AA127 N3:R3 Y13 D63:F71 D73:F81 D83:F85 D86:E91 F86:F92 D93:F101" name="LAS"/>
+    <protectedRange sqref="J2:L3 D2:F3 H5:L5 D14:F21 D23:F31 D33:F41 H33:I41 D43:F51 H43:I51 D53:F61 H53:I61 H63:I71 H73:I81 H83:I91 H93:I101 D103:F110 H103:I110 D112:F127 H112:I127 N127:Q127 H14:I21 H23:I31 H6:I12 Q112:R112 P2:R2 V2:X3 N13:P126 T13:V127 J6:J127 D5:F12 N4:P4 T4:V4 J4 Z4:AA127 N3:R3 Y13 D63:F71 D73:F81 D83:F85 D86:E91 F86:F92 D93:F101 K6:L12 K14:L21 K23:L31 K33:L41 K43:L51 K53:L61 K63:L71 K73:L81 K83:L91 K93:L101 K103:L110 K112:L127 N5:R12 Q14:R21 Q23:R31 Q33:R41 Q43:R51 Q53:R61 Q63:R71 Q73:R81 Q83:R91 Q93:R101 Q103:R110 Q113:Q126 R113:R127 T5:X12 W14:X21 W23:X31 W33:X41 W43:X51 W53:X61 W63:X71 W73:X81 W83:X91 W93:X101 W103:X110 W112:X127" name="LAS"/>
     <protectedRange sqref="G2:I3 M2:O2 S2:U3 Y2:AA3 G112:G127 M112:M127 S112:S127 Y112:Y127 G5:G12 M5:M12 S4:S110 Y5:Y12 G14:G21 M14:M110 M3 Y14:Y110 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" name="SOURCE"/>
   </protectedRanges>
   <dataConsolidate/>
@@ -13650,15 +13467,18 @@
     <mergeCell ref="P1:U1"/>
     <mergeCell ref="V1:AA1"/>
   </mergeCells>
-  <dataValidations count="3">
+  <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S112:S127 M112:M127 Y112:Y127 G112:G127" xr:uid="{8289B4A9-982E-4C7E-A8E2-4BF3404561DB}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X23:X31 X33:X41 X43:X51 X63:X71 X73:X81 X53:X61 L112:L127 X83:X91 X93:X101 X14:X21 X5:X12 L23:L31 L33:L41 L43:L51 L63:L71 L73:L81 L53:L61 R112:R127 L83:L91 L93:L101 L14:L21 L5:L12 R23:R31 R33:R41 R43:R51 R63:R71 R73:R81 R53:R61 F112:F127 R83:R91 R93:R101 R14:R21 R5:R12 F23:F31 F33:F41 F43:F51 X112:X127 F63:F71 F53:F61 F5:F12 F73:F81 F14:F21 F103:F110 R103:R110 L103:L110 X103:X110 F83:F101" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F112:F127 F63:F71 F53:F61 F14:F21 F5:F12 F23:F31 F43:F51 F73:F81 F103:F110 F83:F101 F33:F41" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
       <formula1>"2024,2025"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M14:M110 Y14:Y110 S4:S110 G5:G12 M5:M12 Y5:Y12 G14:G21 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L5:L12 L14:L21 L23:L31 L33:L41 L43:L51 L53:L61 L63:L71 L73:L81 L83:L91 L93:L101 L103:L110 L112:L127 R5:R12 R14:R21 R23:R31 R33:R41 R43:R51 R53:R61 R63:R71 R73:R81 R83:R91 R93:R101 R103:R110 R112:R127 X5:X12 X14:X21 X23:X31 X33:X41 X43:X51 X53:X61 X63:X71 X73:X81 X83:X91 X93:X101 X103:X110 X112:X127" xr:uid="{B54283C8-D9F7-4CA0-AC01-FCDE3BD45FA9}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13673,7 +13493,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F176E3C0-9A94-45E4-9AFD-70DF8ABE5E5A}">
-  <dimension ref="A1:AB170"/>
+  <dimension ref="A1:AB140"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -13888,7 +13708,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="19.149999999999999">
+    <row r="4" spans="1:27" ht="19.5">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -13957,7 +13777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="19.149999999999999">
+    <row r="5" spans="1:27" ht="19.5">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -14026,7 +13846,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="19.149999999999999">
+    <row r="6" spans="1:27" ht="19.5">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -14095,7 +13915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="19.149999999999999">
+    <row r="7" spans="1:27" ht="19.5">
       <c r="A7" s="1">
         <v>1</v>
       </c>
@@ -14164,7 +13984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="19.149999999999999">
+    <row r="8" spans="1:27" ht="19.5">
       <c r="A8" s="1">
         <v>1</v>
       </c>
@@ -14233,7 +14053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="19.149999999999999">
+    <row r="9" spans="1:27" ht="19.5">
       <c r="A9" s="1">
         <v>1</v>
       </c>
@@ -14302,7 +14122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="19.149999999999999">
+    <row r="10" spans="1:27" ht="19.5">
       <c r="A10" s="1">
         <v>1</v>
       </c>
@@ -14441,7 +14261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="19.149999999999999">
+    <row r="13" spans="1:27" ht="19.5">
       <c r="A13" s="1">
         <v>2</v>
       </c>
@@ -14510,7 +14330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="19.149999999999999">
+    <row r="14" spans="1:27" ht="19.5">
       <c r="A14" s="1">
         <v>2</v>
       </c>
@@ -14579,7 +14399,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="19.149999999999999">
+    <row r="15" spans="1:27" ht="19.5">
       <c r="A15" s="1">
         <v>2</v>
       </c>
@@ -14648,7 +14468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="19.149999999999999">
+    <row r="16" spans="1:27" ht="19.5">
       <c r="A16" s="1">
         <v>2</v>
       </c>
@@ -14717,7 +14537,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="19.149999999999999">
+    <row r="17" spans="1:27" ht="19.5">
       <c r="A17" s="1">
         <v>2</v>
       </c>
@@ -14786,7 +14606,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="19.149999999999999">
+    <row r="18" spans="1:27" ht="19.5">
       <c r="A18" s="1">
         <v>2</v>
       </c>
@@ -14855,7 +14675,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="19.149999999999999">
+    <row r="19" spans="1:27" ht="19.5">
       <c r="A19" s="1">
         <v>2</v>
       </c>
@@ -14994,7 +14814,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="19.149999999999999">
+    <row r="22" spans="1:27" ht="19.5">
       <c r="A22" s="1">
         <v>3</v>
       </c>
@@ -15063,7 +14883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="19.149999999999999">
+    <row r="23" spans="1:27" ht="19.5">
       <c r="A23" s="1">
         <v>3</v>
       </c>
@@ -15132,7 +14952,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="19.149999999999999">
+    <row r="24" spans="1:27" ht="19.5">
       <c r="A24" s="1">
         <v>3</v>
       </c>
@@ -15201,7 +15021,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="19.149999999999999">
+    <row r="25" spans="1:27" ht="19.5">
       <c r="A25" s="1">
         <v>3</v>
       </c>
@@ -15270,7 +15090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="19.149999999999999">
+    <row r="26" spans="1:27" ht="19.5">
       <c r="A26" s="1">
         <v>3</v>
       </c>
@@ -15339,7 +15159,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="19.149999999999999">
+    <row r="27" spans="1:27" ht="19.5">
       <c r="A27" s="1">
         <v>3</v>
       </c>
@@ -15408,7 +15228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="19.149999999999999">
+    <row r="28" spans="1:27" ht="19.5">
       <c r="A28" s="1">
         <v>3</v>
       </c>
@@ -15477,7 +15297,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="19.149999999999999">
+    <row r="29" spans="1:27" ht="19.5">
       <c r="A29" s="1">
         <v>3</v>
       </c>
@@ -15616,7 +15436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:27" ht="19.149999999999999">
+    <row r="32" spans="1:27" ht="19.5">
       <c r="A32" s="1">
         <v>4</v>
       </c>
@@ -15685,7 +15505,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:27" ht="19.149999999999999">
+    <row r="33" spans="1:27" ht="19.5">
       <c r="A33" s="1">
         <v>4</v>
       </c>
@@ -15754,7 +15574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="19.149999999999999">
+    <row r="34" spans="1:27" ht="19.5">
       <c r="A34" s="1">
         <v>4</v>
       </c>
@@ -15823,7 +15643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="19.149999999999999">
+    <row r="35" spans="1:27" ht="38.25">
       <c r="A35" s="1">
         <v>4</v>
       </c>
@@ -15892,7 +15712,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="19.149999999999999">
+    <row r="36" spans="1:27" ht="19.5">
       <c r="A36" s="1">
         <v>4</v>
       </c>
@@ -15961,7 +15781,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="19.149999999999999">
+    <row r="37" spans="1:27" ht="19.5">
       <c r="A37" s="37">
         <v>4</v>
       </c>
@@ -16030,7 +15850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="19.149999999999999">
+    <row r="38" spans="1:27" ht="19.5">
       <c r="A38" s="1">
         <v>4</v>
       </c>
@@ -16099,7 +15919,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="19.149999999999999">
+    <row r="39" spans="1:27" ht="19.5">
       <c r="A39" s="1">
         <v>4</v>
       </c>
@@ -16168,7 +15988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="19.149999999999999">
+    <row r="40" spans="1:27" ht="19.5">
       <c r="A40" s="37">
         <v>4</v>
       </c>
@@ -16237,7 +16057,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="19.149999999999999">
+    <row r="41" spans="1:27" ht="19.5">
       <c r="A41" s="1">
         <v>4</v>
       </c>
@@ -16376,7 +16196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="19.149999999999999">
+    <row r="44" spans="1:27" ht="19.5">
       <c r="A44" s="1">
         <v>5</v>
       </c>
@@ -16445,7 +16265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="19.149999999999999">
+    <row r="45" spans="1:27" ht="19.5">
       <c r="A45" s="1">
         <v>5</v>
       </c>
@@ -16514,7 +16334,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="19.149999999999999">
+    <row r="46" spans="1:27" ht="19.5">
       <c r="A46" s="1">
         <v>5</v>
       </c>
@@ -16583,7 +16403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="19.149999999999999">
+    <row r="47" spans="1:27" ht="38.25">
       <c r="A47" s="1">
         <v>5</v>
       </c>
@@ -16652,7 +16472,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="19.149999999999999">
+    <row r="48" spans="1:27" ht="19.5">
       <c r="A48" s="1">
         <v>5</v>
       </c>
@@ -16721,7 +16541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:27" ht="19.149999999999999">
+    <row r="49" spans="1:27" ht="19.5">
       <c r="A49" s="37">
         <v>5</v>
       </c>
@@ -16790,7 +16610,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="19.149999999999999">
+    <row r="50" spans="1:27" ht="19.5">
       <c r="A50" s="1">
         <v>5</v>
       </c>
@@ -16859,7 +16679,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="19.149999999999999">
+    <row r="51" spans="1:27" ht="19.5">
       <c r="A51" s="1">
         <v>5</v>
       </c>
@@ -16928,7 +16748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:27" ht="19.149999999999999">
+    <row r="52" spans="1:27" ht="19.5">
       <c r="A52" s="37">
         <v>5</v>
       </c>
@@ -16997,7 +16817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:27" ht="19.149999999999999">
+    <row r="53" spans="1:27" ht="19.5">
       <c r="A53" s="1">
         <v>5</v>
       </c>
@@ -17067,7 +16887,7 @@
       </c>
     </row>
     <row r="54" spans="1:27" s="7" customFormat="1"/>
-    <row r="55" spans="1:27" ht="19.149999999999999">
+    <row r="55" spans="1:27" ht="19.5">
       <c r="A55" s="1">
         <v>6</v>
       </c>
@@ -17110,7 +16930,7 @@
         <v>0</v>
       </c>
       <c r="Q55" s="5"/>
-      <c r="R55" s="1"/>
+      <c r="R55" s="32"/>
       <c r="S55" s="5"/>
       <c r="T55" s="5">
         <f t="shared" si="4"/>
@@ -17136,7 +16956,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:27" ht="19.149999999999999">
+    <row r="56" spans="1:27" ht="19.5">
       <c r="A56" s="1">
         <v>6</v>
       </c>
@@ -17179,8 +16999,8 @@
         <v>0</v>
       </c>
       <c r="Q56" s="5"/>
-      <c r="R56" s="1"/>
-      <c r="S56" s="5"/>
+      <c r="R56" s="32"/>
+      <c r="S56" s="1"/>
       <c r="T56" s="5">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -17205,7 +17025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:27" ht="19.149999999999999">
+    <row r="57" spans="1:27" ht="19.5">
       <c r="A57" s="1">
         <v>6</v>
       </c>
@@ -17248,7 +17068,7 @@
         <v>0</v>
       </c>
       <c r="Q57" s="5"/>
-      <c r="R57" s="1"/>
+      <c r="R57" s="32"/>
       <c r="S57" s="5"/>
       <c r="T57" s="5">
         <f t="shared" si="4"/>
@@ -17274,7 +17094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:27" ht="19.149999999999999">
+    <row r="58" spans="1:27" ht="19.5">
       <c r="A58" s="1">
         <v>6</v>
       </c>
@@ -17317,7 +17137,7 @@
         <v>0</v>
       </c>
       <c r="Q58" s="5"/>
-      <c r="R58" s="1"/>
+      <c r="R58" s="32"/>
       <c r="S58" s="5"/>
       <c r="T58" s="5">
         <f t="shared" si="4"/>
@@ -17343,7 +17163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:27" ht="19.149999999999999">
+    <row r="59" spans="1:27" ht="38.25">
       <c r="A59" s="1">
         <v>6</v>
       </c>
@@ -17386,7 +17206,7 @@
         <v>0</v>
       </c>
       <c r="Q59" s="5"/>
-      <c r="R59" s="1"/>
+      <c r="R59" s="32"/>
       <c r="S59" s="5"/>
       <c r="T59" s="5">
         <f t="shared" si="4"/>
@@ -17412,7 +17232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:27" ht="19.149999999999999">
+    <row r="60" spans="1:27" ht="19.5">
       <c r="A60" s="1">
         <v>6</v>
       </c>
@@ -17455,7 +17275,7 @@
         <v>0</v>
       </c>
       <c r="Q60" s="5"/>
-      <c r="R60" s="1"/>
+      <c r="R60" s="32"/>
       <c r="S60" s="5"/>
       <c r="T60" s="5">
         <f t="shared" si="4"/>
@@ -17481,7 +17301,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:27" ht="19.149999999999999">
+    <row r="61" spans="1:27" ht="19.5">
       <c r="A61" s="37">
         <v>6</v>
       </c>
@@ -17524,7 +17344,7 @@
         <v>0</v>
       </c>
       <c r="Q61" s="5"/>
-      <c r="R61" s="1"/>
+      <c r="R61" s="32"/>
       <c r="S61" s="5"/>
       <c r="T61" s="5">
         <f>IF((P61-Q61)&lt;0,0,(P61-Q61))</f>
@@ -17550,7 +17370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:27" ht="19.149999999999999">
+    <row r="62" spans="1:27" ht="19.5">
       <c r="A62" s="1">
         <v>6</v>
       </c>
@@ -17593,7 +17413,7 @@
         <v>0</v>
       </c>
       <c r="Q62" s="5"/>
-      <c r="R62" s="1"/>
+      <c r="R62" s="32"/>
       <c r="S62" s="5"/>
       <c r="T62" s="5">
         <f t="shared" si="4"/>
@@ -17619,7 +17439,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:27" ht="19.149999999999999">
+    <row r="63" spans="1:27" ht="19.5">
       <c r="A63" s="1">
         <v>6</v>
       </c>
@@ -17662,7 +17482,7 @@
         <v>0</v>
       </c>
       <c r="Q63" s="5"/>
-      <c r="R63" s="1"/>
+      <c r="R63" s="32"/>
       <c r="S63" s="5"/>
       <c r="T63" s="5">
         <f t="shared" si="4"/>
@@ -17688,7 +17508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:27" ht="19.149999999999999">
+    <row r="64" spans="1:27" ht="19.5">
       <c r="A64" s="37">
         <v>6</v>
       </c>
@@ -17731,7 +17551,7 @@
         <v>0</v>
       </c>
       <c r="Q64" s="5"/>
-      <c r="R64" s="1"/>
+      <c r="R64" s="32"/>
       <c r="S64" s="5"/>
       <c r="T64" s="5">
         <f>IF((P64-Q64)&lt;0,0,(P64-Q64))</f>
@@ -17757,7 +17577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:27" ht="19.149999999999999">
+    <row r="65" spans="1:27" ht="19.5">
       <c r="A65" s="1">
         <v>6</v>
       </c>
@@ -17800,7 +17620,7 @@
         <v>0</v>
       </c>
       <c r="Q65" s="5"/>
-      <c r="R65" s="1"/>
+      <c r="R65" s="32"/>
       <c r="S65" s="5"/>
       <c r="T65" s="5">
         <f t="shared" si="4"/>
@@ -21155,7 +20975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:28" ht="19.149999999999999">
+    <row r="116" spans="1:28" ht="19.5">
       <c r="A116" s="1" t="s">
         <v>23</v>
       </c>
@@ -21224,7 +21044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:28" ht="19.149999999999999">
+    <row r="117" spans="1:28" ht="19.5">
       <c r="A117" s="1" t="s">
         <v>23</v>
       </c>
@@ -21293,7 +21113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:28" ht="19.149999999999999">
+    <row r="118" spans="1:28" ht="19.5">
       <c r="A118" s="1" t="s">
         <v>23</v>
       </c>
@@ -21362,7 +21182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:28" ht="38.450000000000003">
+    <row r="119" spans="1:28" ht="38.25">
       <c r="A119" s="1" t="s">
         <v>23</v>
       </c>
@@ -21431,7 +21251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:28" ht="19.149999999999999">
+    <row r="120" spans="1:28" ht="38.25">
       <c r="A120" s="1" t="s">
         <v>23</v>
       </c>
@@ -21500,7 +21320,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:28" ht="38.450000000000003">
+    <row r="121" spans="1:28" ht="57.75">
       <c r="A121" s="1" t="s">
         <v>23</v>
       </c>
@@ -21569,7 +21389,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:28" ht="38.450000000000003">
+    <row r="122" spans="1:28" ht="38.25">
       <c r="A122" s="1" t="s">
         <v>23</v>
       </c>
@@ -22149,191 +21969,11 @@
       <c r="AA140" s="7"/>
       <c r="AB140" s="7"/>
     </row>
-    <row r="141" spans="1:28">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="1:28">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="1:28">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="1:28">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="158" spans="10:10">
-      <c r="J158" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="159" spans="10:10">
-      <c r="J159" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="160" spans="10:10">
-      <c r="J160" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="161" spans="10:10">
-      <c r="J161" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="162" spans="10:10">
-      <c r="J162" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="163" spans="10:10">
-      <c r="J163" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="164" spans="10:10">
-      <c r="J164" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="165" spans="10:10">
-      <c r="J165" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="166" spans="10:10">
-      <c r="J166" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="167" spans="10:10">
-      <c r="J167" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="168" spans="10:10">
-      <c r="J168" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="169" spans="10:10">
-      <c r="J169" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="170" spans="10:10">
-      <c r="J170" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C2:C10 C12:C19 C21:C29 C31:C41 C43:C53 C55:C65 C67:C77 C79:C89 C115:C122 C103:C113 C91:C101" name="Textbooks"/>
-    <protectedRange sqref="J2:L2 D2:F10 D12:F19 D21:F29 D31:F41 D43:F53 D55:F65 D115:F122 P2:R10 N3:O10 V2:X10 T3:U10 N12:R19 T12:X19 H3:L10 Z3:AA10 Z12:AA19 H12:L19 N21:R29 T21:X29 Z21:AA29 H21:L29 T31:X41 Z31:AA41 H31:L41 T43:X53 Z43:AA53 H43:L53 T55:X65 Z55:AA65 H55:L65 T67:X77 Z67:AA77 H67:L77 T79:X89 Z79:AA89 H79:L89 T91:X101 Z91:AA101 H91:L101 T103:X113 Z103:AA113 H103:L113 N115:R122 T115:X122 Z115:AA122 H115:L122 N31:R41 N43:R53 N55:R65 N67:R77 N79:R89 N91:R101 N103:R113 D67:F77 D79:F89 D91:F101 D103:F113" name="LAS"/>
-    <protectedRange sqref="G2:I2 M2:O2 S2:U2 Y2:AA2 G3:G10 M3:M10 S3:S10 Y3:Y10 Y12:Y19 G12:G19 M12:M19 S12:S19 Y21:Y29 G21:G29 M21:M29 S21:S29 Y31:Y41 G31:G41 M31:M41 S31:S41 Y43:Y53 G43:G53 M43:M53 S43:S53 Y55:Y65 G55:G65 M55:M65 S55:S65 Y67:Y77 M67:M77 S67:S77 Y79:Y89 M79:M89 S79:S89 Y91:Y101 M91:M101 S91:S101 Y103:Y113 M103:M113 S103:S113 Y115:Y122 G115:G122 M115:M122 S115:S122 G67:G77 G79:G89 G91:G101 G103:G113" name="SOURCE"/>
+    <protectedRange sqref="J2:L2 D2:F10 D12:F19 D21:F29 D31:F41 D43:F53 D55:F65 D115:F122 N3:O10 T3:U10 Z3:AA10 Z12:AA19 Z21:AA29 Z31:AA41 Z43:AA53 Z55:AA65 Z67:AA77 Z79:AA89 Z91:AA101 Z103:AA113 Z115:AA122 S56 D67:F77 D79:F89 D91:F101 D103:F113 H3:L10 H12:L19 H21:L29 H31:L41 H43:L53 H55:L65 H67:L77 H79:L89 H91:L101 H103:L113 H115:L122 P2:R10 N12:R19 N21:R29 N31:R41 N43:R53 N55:Q65 N67:R77 N79:R89 N91:R101 N103:R113 N115:R122 V2:X10 T12:X19 T21:X29 T31:X41 T43:X53 T55:X65 T67:X77 T79:X89 T91:X101 T103:X113 T115:X122" name="LAS"/>
+    <protectedRange sqref="G2:I2 M2:O2 S2:U2 Y2:AA2 G3:G10 M3:M10 S3:S10 Y3:Y10 Y12:Y19 G12:G19 M12:M19 S12:S19 Y21:Y29 G21:G29 M21:M29 S21:S29 Y31:Y41 G31:G41 M31:M41 S31:S41 Y43:Y53 G43:G53 M43:M53 S43:S53 Y55:Y65 G55:G65 M55:M65 G103:G113 Y67:Y77 M67:M77 S67:S77 Y79:Y89 M79:M89 S79:S89 Y91:Y101 M91:M101 S91:S101 Y103:Y113 M103:M113 S103:S113 Y115:Y122 G115:G122 M115:M122 S115:S122 G67:G77 G79:G89 G91:G101 S55 S57:S65" name="SOURCE"/>
   </protectedRanges>
   <dataConsolidate/>
   <mergeCells count="4">
@@ -22342,12 +21982,18 @@
     <mergeCell ref="P1:U1"/>
     <mergeCell ref="V1:AA1"/>
   </mergeCells>
-  <dataValidations count="2">
+  <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S115:S122 Y115:Y122 G115:G122 Y3:Y10 S3:S10 M3:M10 G3:G10 G12:G19 Y12:Y19 S12:S19 M12:M19 M21:M29 G21:G29 Y21:Y29 S21:S29 S31:S41 M31:M41 G31:G41 Y31:Y41 Y43:Y53 S43:S53 M43:M53 G43:G53 G55:G65 Y55:Y65 S55:S65 M55:M65 M67:M77 M115:M122 Y67:Y77 S67:S77 S79:S89 M79:M89 G67:G77 Y79:Y89 Y91:Y101 S91:S101 M91:M101 G79:G89 G91:G101 Y103:Y113 S103:S113 M103:M113 G103:G113" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X21:X29 X31:X41 X43:X53 X67:X77 X79:X89 X55:X65 X91:X101 X103:X113 X12:X19 X3:X10 L21:L29 L31:L41 L43:L53 L67:L77 L79:L89 L55:L65 L91:L101 L103:L113 L12:L19 L3:L10 R21:R29 R31:R41 R43:R53 R67:R77 R79:R89 R55:R65 R91:R101 R103:R113 R12:R19 R3:R10 F21:F29 F31:F41 F43:F53 F91:F101 F67:F77 F55:F65 F3:F10 F79:F89 X115:X122 F12:F19 F115:F122 R115:R122 L115:L122 F103:F113" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F43:F53 F21:F29 F103:F113 F67:F77 F91:F101 F55:F65 F3:F10 F31:F41 S56 R43 F115:F122 F12:F19 F79:F89" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
       <formula1>"2024,2025"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L3:L10 L12:L19 L21:L29 L31:L41 L43:L53 L55:L65 L67:L77 L79:L89 L91:L101 L103:L113 L115:L122 R3:R10 R12:R19 R21:R29 R31:R41 R44:R53 R67:R77 R79:R89 R91:R101 R103:R113 R115:R122 X3:X10 X12:X19 X21:X29 X31:X41 X43:X53 X55:X65 X67:X77 X79:X89 X91:X101 X103:X113 X115:X122" xr:uid="{36E140AE-B81F-414C-A913-90DC918462F4}">
+      <formula1>"2024,2025,2026"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R55:R65" xr:uid="{7E5B4B45-76E2-4B3A-9388-7EC4FD955BFD}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
